--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_Regresie_Refinat.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_Regresie_Refinat.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,16 +389,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>-9.659038055863411</v>
+        <v>-6.190750338884286</v>
       </c>
       <c r="C2">
-        <v>3.161690870145732</v>
+        <v>4.588014587066205</v>
       </c>
       <c r="D2">
-        <v>-3.055022914184585</v>
+        <v>-1.349331006125451</v>
       </c>
       <c r="E2">
-        <v>0.005288391646717567</v>
+        <v>0.1876717283466892</v>
       </c>
     </row>
     <row r="3">
@@ -408,16 +408,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.335889711157555</v>
+        <v>0.8148457939050476</v>
       </c>
       <c r="C3">
-        <v>0.2789334772685458</v>
+        <v>0.4471344216325375</v>
       </c>
       <c r="D3">
-        <v>4.789277085845866</v>
+        <v>1.822373215933488</v>
       </c>
       <c r="E3">
-        <v>6.432858237137776E-05</v>
+        <v>0.07872584110426717</v>
       </c>
     </row>
     <row r="4">
@@ -427,16 +427,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.056287725961854</v>
+        <v>0.6148598162070217</v>
       </c>
       <c r="C4">
-        <v>0.2034900317709942</v>
+        <v>0.262038768131615</v>
       </c>
       <c r="D4">
-        <v>5.19085734455332</v>
+        <v>2.346445988092091</v>
       </c>
       <c r="E4">
-        <v>2.276265250149115E-05</v>
+        <v>0.02599686641220045</v>
       </c>
     </row>
     <row r="5">
@@ -446,54 +446,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.09715251594930936</v>
+        <v>0.4455444553104576</v>
       </c>
       <c r="C5">
-        <v>0.2433738321554104</v>
+        <v>0.2273395476368692</v>
       </c>
       <c r="D5">
-        <v>0.3991904761859155</v>
+        <v>1.95981939764448</v>
       </c>
       <c r="E5">
-        <v>0.693142529500584</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ln_Densitate</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.02634380359892114</v>
-      </c>
-      <c r="C6">
-        <v>0.1654213384679246</v>
-      </c>
-      <c r="D6">
-        <v>0.1592527532596965</v>
-      </c>
-      <c r="E6">
-        <v>0.8747493457871336</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Membru_UE</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>-0.01781944835050439</v>
-      </c>
-      <c r="C7">
-        <v>0.6506316438232214</v>
-      </c>
-      <c r="D7">
-        <v>-0.02738792144475836</v>
-      </c>
-      <c r="E7">
-        <v>0.9783677903202626</v>
+        <v>0.05968990588246588</v>
       </c>
     </row>
   </sheetData>
@@ -570,40 +532,40 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.8575285438909718</v>
+        <v>0.4828585465185094</v>
       </c>
       <c r="B2">
-        <v>0.8290342526691661</v>
+        <v>0.4293611547790448</v>
       </c>
       <c r="C2">
-        <v>0.8083425179975747</v>
+        <v>1.67121745015433</v>
       </c>
       <c r="D2">
-        <v>30.09474905747913</v>
+        <v>9.025833425114612</v>
       </c>
       <c r="E2">
-        <v>8.186504101716595E-10</v>
+        <v>0.0002226806782189529</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>-34.05701668725054</v>
+        <v>-61.64020633193189</v>
       </c>
       <c r="H2">
-        <v>82.11403337450108</v>
+        <v>133.2804126638638</v>
       </c>
       <c r="I2">
-        <v>92.1519438058971</v>
+        <v>140.7629504711962</v>
       </c>
       <c r="J2">
-        <v>16.33544066006649</v>
+        <v>80.99606520530986</v>
       </c>
       <c r="K2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
